--- a/docs/enterprise-context/synthetic/arcturus/13-initiative-portfolio.xlsx
+++ b/docs/enterprise-context/synthetic/arcturus/13-initiative-portfolio.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="306">
   <si>
     <t>Dataset</t>
   </si>
@@ -537,100 +537,103 @@
     <t>CI-APP-SERVICENOW|CI-APP-001</t>
   </si>
   <si>
+    <t>CON-NCINO-2026</t>
+  </si>
+  <si>
+    <t>POL-010|POL-013</t>
+  </si>
+  <si>
+    <t>INIT-10</t>
+  </si>
+  <si>
+    <t>INIT-011</t>
+  </si>
+  <si>
+    <t>AI Model Governance Workflow 2</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>CI-SEC-OKTA|CI-SVC-002</t>
+  </si>
+  <si>
+    <t>CON-SNOW-2026</t>
+  </si>
+  <si>
+    <t>POL-011|POL-014</t>
+  </si>
+  <si>
+    <t>INIT-11</t>
+  </si>
+  <si>
+    <t>INIT-012</t>
+  </si>
+  <si>
+    <t>Credit Decisioning Platform 2</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>CI-CLOUD-AWS-PROD|CI-DATA-003</t>
+  </si>
+  <si>
+    <t>CON-MICROSOFT-2026</t>
+  </si>
+  <si>
+    <t>POL-012|POL-015</t>
+  </si>
+  <si>
+    <t>INIT-12</t>
+  </si>
+  <si>
+    <t>INIT-013</t>
+  </si>
+  <si>
+    <t>Regulatory Reporting Automation 2</t>
+  </si>
+  <si>
+    <t>CI-CLOUD-AZURE-PROD|CI-APP-004</t>
+  </si>
+  <si>
+    <t>CON-AWS-2026</t>
+  </si>
+  <si>
+    <t>POL-013|POL-016</t>
+  </si>
+  <si>
+    <t>INIT-13</t>
+  </si>
+  <si>
+    <t>INIT-014</t>
+  </si>
+  <si>
+    <t>Fraud Operations Modernization 2</t>
+  </si>
+  <si>
+    <t>CI-APP-MUREX|CI-SVC-005</t>
+  </si>
+  <si>
+    <t>CON-AZURE-2026</t>
+  </si>
+  <si>
+    <t>POL-014|POL-017</t>
+  </si>
+  <si>
+    <t>INIT-14</t>
+  </si>
+  <si>
+    <t>INIT-015</t>
+  </si>
+  <si>
+    <t>Cloud Controls Remediation 2</t>
+  </si>
+  <si>
+    <t>CI-APP-SAS-MRM|CI-DATA-006</t>
+  </si>
+  <si>
     <t>CON-DATABRICKS-2026</t>
-  </si>
-  <si>
-    <t>POL-010|POL-013</t>
-  </si>
-  <si>
-    <t>INIT-10</t>
-  </si>
-  <si>
-    <t>INIT-011</t>
-  </si>
-  <si>
-    <t>AI Model Governance Workflow 2</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>CI-SEC-OKTA|CI-SVC-002</t>
-  </si>
-  <si>
-    <t>CON-SNOW-2026</t>
-  </si>
-  <si>
-    <t>POL-011|POL-014</t>
-  </si>
-  <si>
-    <t>INIT-11</t>
-  </si>
-  <si>
-    <t>INIT-012</t>
-  </si>
-  <si>
-    <t>Credit Decisioning Platform 2</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>CI-CLOUD-AWS-PROD|CI-DATA-003</t>
-  </si>
-  <si>
-    <t>CON-MICROSOFT-2026</t>
-  </si>
-  <si>
-    <t>POL-012|POL-015</t>
-  </si>
-  <si>
-    <t>INIT-12</t>
-  </si>
-  <si>
-    <t>INIT-013</t>
-  </si>
-  <si>
-    <t>Regulatory Reporting Automation 2</t>
-  </si>
-  <si>
-    <t>CI-CLOUD-AZURE-PROD|CI-APP-004</t>
-  </si>
-  <si>
-    <t>CON-AWS-2026</t>
-  </si>
-  <si>
-    <t>POL-013|POL-016</t>
-  </si>
-  <si>
-    <t>INIT-13</t>
-  </si>
-  <si>
-    <t>INIT-014</t>
-  </si>
-  <si>
-    <t>Fraud Operations Modernization 2</t>
-  </si>
-  <si>
-    <t>CI-APP-MUREX|CI-SVC-005</t>
-  </si>
-  <si>
-    <t>CON-AZURE-2026</t>
-  </si>
-  <si>
-    <t>POL-014|POL-017</t>
-  </si>
-  <si>
-    <t>INIT-14</t>
-  </si>
-  <si>
-    <t>INIT-015</t>
-  </si>
-  <si>
-    <t>Cloud Controls Remediation 2</t>
-  </si>
-  <si>
-    <t>CI-APP-SAS-MRM|CI-DATA-006</t>
   </si>
   <si>
     <t>POL-015|POL-018</t>
@@ -2659,16 +2662,16 @@
         <v>205</v>
       </c>
       <c r="K16" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M16" t="s">
         <v>92</v>
       </c>
       <c r="N16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O16" t="s">
         <v>92</v>
@@ -2688,10 +2691,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" t="s">
         <v>118</v>
@@ -2715,19 +2718,19 @@
         <v>88</v>
       </c>
       <c r="J17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M17" t="s">
         <v>92</v>
       </c>
       <c r="N17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O17" t="s">
         <v>92</v>
@@ -2747,10 +2750,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
         <v>82</v>
@@ -2774,19 +2777,19 @@
         <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s">
         <v>92</v>
       </c>
       <c r="N18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O18" t="s">
         <v>92</v>
@@ -2806,10 +2809,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
         <v>97</v>
@@ -2833,19 +2836,19 @@
         <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s">
         <v>92</v>
       </c>
       <c r="N19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
         <v>92</v>
@@ -2865,10 +2868,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
         <v>108</v>
@@ -2892,19 +2895,19 @@
         <v>88</v>
       </c>
       <c r="J20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s">
         <v>92</v>
       </c>
       <c r="N20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O20" t="s">
         <v>92</v>
@@ -2924,10 +2927,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C21" t="s">
         <v>118</v>
@@ -2951,19 +2954,19 @@
         <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s">
         <v>92</v>
       </c>
       <c r="N21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O21" t="s">
         <v>92</v>
@@ -2983,10 +2986,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
         <v>82</v>
@@ -3010,19 +3013,19 @@
         <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s">
         <v>92</v>
       </c>
       <c r="N22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O22" t="s">
         <v>92</v>
@@ -3042,10 +3045,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C23" t="s">
         <v>97</v>
@@ -3069,19 +3072,19 @@
         <v>88</v>
       </c>
       <c r="J23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s">
         <v>92</v>
       </c>
       <c r="N23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O23" t="s">
         <v>92</v>
@@ -3101,10 +3104,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
         <v>108</v>
@@ -3128,19 +3131,19 @@
         <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s">
         <v>92</v>
       </c>
       <c r="N24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s">
         <v>92</v>
@@ -3160,10 +3163,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
         <v>118</v>
@@ -3187,19 +3190,19 @@
         <v>88</v>
       </c>
       <c r="J25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s">
         <v>92</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
         <v>92</v>
@@ -3219,10 +3222,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" t="s">
         <v>82</v>
@@ -3246,19 +3249,19 @@
         <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s">
         <v>92</v>
       </c>
       <c r="N26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O26" t="s">
         <v>92</v>
@@ -3278,10 +3281,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" t="s">
         <v>97</v>
@@ -3305,19 +3308,19 @@
         <v>88</v>
       </c>
       <c r="J27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s">
         <v>92</v>
       </c>
       <c r="N27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s">
         <v>92</v>
@@ -3337,10 +3340,10 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
         <v>108</v>
@@ -3364,19 +3367,19 @@
         <v>88</v>
       </c>
       <c r="J28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K28" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s">
         <v>92</v>
       </c>
       <c r="N28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O28" t="s">
         <v>92</v>
@@ -3396,10 +3399,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C29" t="s">
         <v>118</v>
@@ -3423,19 +3426,19 @@
         <v>88</v>
       </c>
       <c r="J29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K29" t="s">
         <v>90</v>
       </c>
       <c r="L29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s">
         <v>92</v>
       </c>
       <c r="N29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O29" t="s">
         <v>92</v>
@@ -3455,10 +3458,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" t="s">
         <v>82</v>
@@ -3482,19 +3485,19 @@
         <v>88</v>
       </c>
       <c r="J30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K30" t="s">
         <v>103</v>
       </c>
       <c r="L30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s">
         <v>92</v>
       </c>
       <c r="N30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O30" t="s">
         <v>92</v>
@@ -3514,10 +3517,10 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" t="s">
         <v>97</v>
@@ -3541,19 +3544,19 @@
         <v>88</v>
       </c>
       <c r="J31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K31" t="s">
         <v>113</v>
       </c>
       <c r="L31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s">
         <v>92</v>
       </c>
       <c r="N31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O31" t="s">
         <v>92</v>
@@ -3573,10 +3576,10 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C32" t="s">
         <v>108</v>
@@ -3600,19 +3603,19 @@
         <v>88</v>
       </c>
       <c r="J32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K32" t="s">
         <v>125</v>
       </c>
       <c r="L32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s">
         <v>92</v>
       </c>
       <c r="N32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O32" t="s">
         <v>92</v>
@@ -3632,10 +3635,10 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C33" t="s">
         <v>118</v>
@@ -3659,19 +3662,19 @@
         <v>88</v>
       </c>
       <c r="J33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K33" t="s">
         <v>133</v>
       </c>
       <c r="L33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s">
         <v>92</v>
       </c>
       <c r="N33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O33" t="s">
         <v>92</v>
